--- a/data/postgres/mvp_strategy_tempates.xlsx
+++ b/data/postgres/mvp_strategy_tempates.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="시트1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시트1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -765,7 +765,7 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>사용자가 매일 취침·기상 시간을 직접 입력하는 수동 기록 방식으로 MVP를 출시하고, PSQI(피츠버그 수면질지수) 같은 무료 표준 설문으로 초기 수면의 질 데이터를 함께 수집하세요.</t>
+          <t>사용자가 매일 취침·기상 시간을 직접 입력하는 수동 기록 방식으로 MVP를 출시하고, PSQI(피츠버그 수면질지수) 같은 표준 설문(상업적 사용 시 유료·허가 필요)으로 초기 수면의 질 데이터를 함께 수집하세요.</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>수면다원검사 같은 정밀 검사는 당장 확보가 어려우니, ISI(불면증 심각도 지수) 같은 무료 표준 설문으로 첫 MVP의 핵심 가설을 먼저 검증하세요.</t>
+          <t>수면다원검사 같은 정밀 검사는 당장 확보가 어려우니, ISI(불면증 심각도 지수) 같은 표준 설문(상업적 사용 시 유료·허가 필요)으로 첫 MVP의 핵심 가설을 먼저 검증하세요.</t>
         </is>
       </c>
     </row>
